--- a/ჟურნალი/7. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - React.xlsx
+++ b/ჟურნალი/7. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - React.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t xml:space="preserve">პროგრამა                     </t>
   </si>
@@ -34,6 +34,9 @@
   </si>
   <si>
     <t>24.10.2026</t>
+  </si>
+  <si>
+    <t>27.10.2026</t>
   </si>
   <si>
     <t xml:space="preserve">მოდული: ვებგვერდის ინტერაქტიულობისა და ეფექტების შემუშავება React-ის საშუალებით;; N 06.1.1.5</t>
@@ -1122,10 +1125,12 @@
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
       <c r="O1" s="7"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="5"/>
+      <c r="P1" s="6">
+        <v>4</v>
+      </c>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="7"/>
       <c r="T1" s="5"/>
       <c r="U1" s="5"/>
       <c r="V1" s="9"/>
@@ -1283,7 +1288,7 @@
       <c r="FR1" s="1"/>
       <c r="FS1" s="11">
         <f>SUM(F1:FQ1)</f>
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" ht="11.25" customHeight="1">
@@ -1324,10 +1329,18 @@
       <c r="O2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
+      <c r="P2" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="R2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="S2" s="13" t="s">
+        <v>6</v>
+      </c>
       <c r="T2" s="12"/>
       <c r="U2" s="12"/>
       <c r="V2" s="12"/>
@@ -1485,7 +1498,7 @@
     </row>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="15" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="15"/>
       <c r="C3" s="15"/>
@@ -1662,11 +1675,11 @@
     </row>
     <row r="4" ht="24.75" customHeight="1">
       <c r="A4" s="15" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="17"/>
       <c r="E4" s="3"/>
@@ -1841,7 +1854,7 @@
     </row>
     <row r="5" ht="16.5" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="18"/>
       <c r="C5" s="19">
@@ -2020,7 +2033,7 @@
     </row>
     <row r="6" ht="16.5" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="19">
@@ -2199,7 +2212,7 @@
     </row>
     <row r="7" ht="16.5" customHeight="1">
       <c r="A7" s="20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="19">
@@ -2218,9 +2231,9 @@
       <c r="N7" s="21"/>
       <c r="O7" s="21"/>
       <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="12"/>
+      <c r="Q7" s="21"/>
+      <c r="R7" s="21"/>
+      <c r="S7" s="21"/>
       <c r="T7" s="12"/>
       <c r="U7" s="12"/>
       <c r="V7" s="12"/>
@@ -2378,7 +2391,7 @@
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="23" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="23"/>
       <c r="C8" s="17">
@@ -2894,13 +2907,13 @@
     </row>
     <row r="9" ht="16.5" customHeight="1">
       <c r="A9" s="24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="26"/>
@@ -3078,10 +3091,10 @@
       <c r="B10" s="25"/>
       <c r="C10" s="27"/>
       <c r="D10" s="25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F10" s="28">
         <v>1</v>
@@ -3593,14 +3606,14 @@
         <v>1</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" s="30">
         <f t="shared" ref="D11:D24" si="0">COUNT(F11:FQ11)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="9"/>
@@ -3615,7 +3628,9 @@
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
       <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
+      <c r="P11" s="9">
+        <v>0</v>
+      </c>
       <c r="Q11" s="9"/>
       <c r="R11" s="9"/>
       <c r="S11" s="9"/>
@@ -3779,14 +3794,14 @@
         <v>2</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D12" s="30">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12" s="31"/>
       <c r="F12" s="9"/>
@@ -3801,10 +3816,14 @@
       <c r="M12" s="9"/>
       <c r="N12" s="9"/>
       <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
+      <c r="P12" s="9">
+        <v>0</v>
+      </c>
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
+      <c r="S12" s="9">
+        <v>0</v>
+      </c>
       <c r="T12" s="9"/>
       <c r="U12" s="9"/>
       <c r="V12" s="9"/>
@@ -3965,14 +3984,14 @@
         <v>3</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13" s="30">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" s="31"/>
       <c r="F13" s="9">
@@ -3999,7 +4018,9 @@
       <c r="O13" s="9">
         <v>0</v>
       </c>
-      <c r="P13" s="9"/>
+      <c r="P13" s="9">
+        <v>0</v>
+      </c>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
       <c r="S13" s="9"/>
@@ -4163,14 +4184,14 @@
         <v>4</v>
       </c>
       <c r="B14" s="29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14" s="30">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" s="31"/>
       <c r="F14" s="9"/>
@@ -4193,7 +4214,9 @@
       <c r="O14" s="9">
         <v>0</v>
       </c>
-      <c r="P14" s="9"/>
+      <c r="P14" s="9">
+        <v>0</v>
+      </c>
       <c r="Q14" s="9"/>
       <c r="R14" s="9"/>
       <c r="S14" s="9"/>
@@ -4357,14 +4380,14 @@
         <v>5</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15" s="30">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E15" s="31"/>
       <c r="F15" s="9"/>
@@ -4373,18 +4396,10 @@
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
       <c r="K15" s="9"/>
-      <c r="L15" s="9">
-        <v>0</v>
-      </c>
-      <c r="M15" s="9">
-        <v>0</v>
-      </c>
-      <c r="N15" s="9">
-        <v>0</v>
-      </c>
-      <c r="O15" s="9">
-        <v>0</v>
-      </c>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
       <c r="P15" s="9"/>
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
@@ -4549,10 +4564,10 @@
         <v>6</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" s="30">
         <f t="shared" si="0"/>
@@ -4735,14 +4750,14 @@
         <v>8</v>
       </c>
       <c r="B17" s="29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" s="30">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="31"/>
       <c r="F17" s="9"/>
@@ -4757,7 +4772,9 @@
       <c r="M17" s="9"/>
       <c r="N17" s="9"/>
       <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
+      <c r="P17" s="9">
+        <v>0</v>
+      </c>
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
       <c r="S17" s="9"/>
@@ -4921,14 +4938,14 @@
         <v>9</v>
       </c>
       <c r="B18" s="29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D18" s="30">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="31"/>
       <c r="F18" s="9"/>
@@ -4943,7 +4960,9 @@
       <c r="M18" s="9"/>
       <c r="N18" s="9"/>
       <c r="O18" s="9"/>
-      <c r="P18" s="9"/>
+      <c r="P18" s="9">
+        <v>0</v>
+      </c>
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
       <c r="S18" s="9"/>
@@ -5107,14 +5126,14 @@
         <v>10</v>
       </c>
       <c r="B19" s="29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D19" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="31"/>
       <c r="F19" s="9"/>
@@ -5127,7 +5146,9 @@
       <c r="M19" s="9"/>
       <c r="N19" s="9"/>
       <c r="O19" s="9"/>
-      <c r="P19" s="9"/>
+      <c r="P19" s="9">
+        <v>0</v>
+      </c>
       <c r="Q19" s="9"/>
       <c r="R19" s="9"/>
       <c r="S19" s="9"/>
@@ -5291,14 +5312,14 @@
         <v>12</v>
       </c>
       <c r="B20" s="33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D20" s="30">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E20" s="31"/>
       <c r="F20" s="9">
@@ -5317,10 +5338,14 @@
       <c r="M20" s="9"/>
       <c r="N20" s="9"/>
       <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
+      <c r="P20" s="9">
+        <v>0</v>
+      </c>
       <c r="Q20" s="9"/>
       <c r="R20" s="9"/>
-      <c r="S20" s="9"/>
+      <c r="S20" s="9">
+        <v>0</v>
+      </c>
       <c r="T20" s="9"/>
       <c r="U20" s="9"/>
       <c r="V20" s="9"/>
@@ -5481,14 +5506,14 @@
         <v>14</v>
       </c>
       <c r="B21" s="29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D21" s="30">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="31"/>
       <c r="F21" s="9"/>
@@ -5503,7 +5528,9 @@
       <c r="M21" s="9"/>
       <c r="N21" s="9"/>
       <c r="O21" s="9"/>
-      <c r="P21" s="9"/>
+      <c r="P21" s="9">
+        <v>0</v>
+      </c>
       <c r="Q21" s="9"/>
       <c r="R21" s="9"/>
       <c r="S21" s="9"/>
@@ -5667,14 +5694,14 @@
         <v>15</v>
       </c>
       <c r="B22" s="29" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D22" s="30">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E22" s="31"/>
       <c r="F22" s="9">
@@ -5693,10 +5720,14 @@
       <c r="M22" s="9"/>
       <c r="N22" s="9"/>
       <c r="O22" s="9"/>
-      <c r="P22" s="9"/>
+      <c r="P22" s="9">
+        <v>0</v>
+      </c>
       <c r="Q22" s="9"/>
       <c r="R22" s="9"/>
-      <c r="S22" s="9"/>
+      <c r="S22" s="9">
+        <v>0</v>
+      </c>
       <c r="T22" s="9"/>
       <c r="U22" s="9"/>
       <c r="V22" s="9"/>
@@ -5857,14 +5888,14 @@
         <v>16</v>
       </c>
       <c r="B23" s="29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D23" s="30">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E23" s="31"/>
       <c r="F23" s="9">
@@ -5891,10 +5922,14 @@
       <c r="O23" s="9">
         <v>0</v>
       </c>
-      <c r="P23" s="9"/>
+      <c r="P23" s="9">
+        <v>0</v>
+      </c>
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
-      <c r="S23" s="9"/>
+      <c r="S23" s="9">
+        <v>0</v>
+      </c>
       <c r="T23" s="9"/>
       <c r="U23" s="9"/>
       <c r="V23" s="9"/>
@@ -6055,14 +6090,14 @@
         <v>17</v>
       </c>
       <c r="B24" s="29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D24" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="31"/>
       <c r="F24" s="9"/>
@@ -6075,7 +6110,9 @@
       <c r="M24" s="9"/>
       <c r="N24" s="9"/>
       <c r="O24" s="9"/>
-      <c r="P24" s="9"/>
+      <c r="P24" s="9">
+        <v>0</v>
+      </c>
       <c r="Q24" s="9"/>
       <c r="R24" s="9"/>
       <c r="S24" s="9"/>
@@ -6348,12 +6385,13 @@
       <c r="DG28" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="356">
+  <mergeCells count="357">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:D2"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:K1"/>
     <mergeCell ref="L1:O1"/>
+    <mergeCell ref="P1:S1"/>
     <mergeCell ref="E2:E7"/>
     <mergeCell ref="F2:F7"/>
     <mergeCell ref="G2:G7"/>
